--- a/data/performance/daily/signal_list_2026-06-15.xlsx
+++ b/data/performance/daily/signal_list_2026-06-15.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 50.0%  (3W / 3L of 6 evaluated)</t>
+          <t>Win Rate: 55.6%  (5W / 4L of 9 evaluated)</t>
         </is>
       </c>
     </row>
@@ -779,6 +779,132 @@
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MGLV.JK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8500</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9125</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BOBA.JK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>336</v>
+      </c>
+      <c r="D12" t="n">
+        <v>330</v>
+      </c>
+      <c r="E12" t="n">
+        <v>350</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BSML.JK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BREAKOUT</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>428</v>
+      </c>
+      <c r="D13" t="n">
+        <v>450</v>
+      </c>
+      <c r="E13" t="n">
+        <v>450</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -795,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -820,7 +946,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 58.9%  (43W / 30L of 73 evaluated)</t>
+          <t>Win Rate: 58.0%  (47W / 34L of 81 evaluated)</t>
         </is>
       </c>
     </row>
@@ -3937,6 +4063,342 @@
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>VICI.JK</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>640</v>
+      </c>
+      <c r="D78" t="n">
+        <v>610</v>
+      </c>
+      <c r="E78" t="n">
+        <v>640</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LUCY.JK</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1490</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1535</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1545</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>NICL.JK</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>610</v>
+      </c>
+      <c r="D80" t="n">
+        <v>630</v>
+      </c>
+      <c r="E80" t="n">
+        <v>665</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OILS.JK</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>202</v>
+      </c>
+      <c r="D81" t="n">
+        <v>197</v>
+      </c>
+      <c r="E81" t="n">
+        <v>204</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CMNT.JK</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>815</v>
+      </c>
+      <c r="D82" t="n">
+        <v>815</v>
+      </c>
+      <c r="E82" t="n">
+        <v>825</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BOBA.JK</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>336</v>
+      </c>
+      <c r="D83" t="n">
+        <v>330</v>
+      </c>
+      <c r="E83" t="n">
+        <v>350</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BSML.JK</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>428</v>
+      </c>
+      <c r="D84" t="n">
+        <v>450</v>
+      </c>
+      <c r="E84" t="n">
+        <v>450</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>HATM.JK</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>330</v>
+      </c>
+      <c r="D85" t="n">
+        <v>340</v>
+      </c>
+      <c r="E85" t="n">
+        <v>346</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-15.xlsx
+++ b/data/performance/daily/signal_list_2026-06-15.xlsx
@@ -1089,7 +1089,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>AKPI.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2890</v>
+        <v>505</v>
       </c>
       <c r="D7" t="n">
-        <v>2880</v>
+        <v>486</v>
       </c>
       <c r="E7" t="n">
-        <v>2880</v>
+        <v>520</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.35</v>
+        <v>2.97</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.35</v>
+        <v>-3.76</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AKPI.JK</t>
+          <t>ARGO.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1140,19 +1140,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>505</v>
+        <v>850</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>840</v>
       </c>
       <c r="E8" t="n">
-        <v>520</v>
+        <v>875</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.76</v>
+        <v>-1.18</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARGO.JK</t>
+          <t>ASJT.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1182,23 +1182,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>850</v>
+        <v>155</v>
       </c>
       <c r="D9" t="n">
-        <v>840</v>
+        <v>159</v>
       </c>
       <c r="E9" t="n">
-        <v>875</v>
+        <v>159</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.58</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASJT.JK</t>
+          <t>BNLI.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1224,23 +1224,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>3220</v>
       </c>
       <c r="D10" t="n">
-        <v>159</v>
+        <v>3210</v>
       </c>
       <c r="E10" t="n">
-        <v>159</v>
+        <v>3450</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.58</v>
+        <v>7.14</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.31</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BNLI.JK</t>
+          <t>BPFI.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3220</v>
+        <v>272</v>
       </c>
       <c r="D11" t="n">
-        <v>3210</v>
+        <v>268</v>
       </c>
       <c r="E11" t="n">
-        <v>3450</v>
+        <v>272</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.31</v>
+        <v>-1.47</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BPFI.JK</t>
+          <t>BUKK.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1308,23 +1308,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>272</v>
+        <v>1005</v>
       </c>
       <c r="D12" t="n">
-        <v>268</v>
+        <v>1255</v>
       </c>
       <c r="E12" t="n">
-        <v>272</v>
+        <v>1255</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>24.88</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>24.88</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BUKK.JK</t>
+          <t>CLPI.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1350,19 +1350,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1005</v>
+        <v>1595</v>
       </c>
       <c r="D13" t="n">
-        <v>1255</v>
+        <v>1650</v>
       </c>
       <c r="E13" t="n">
-        <v>1255</v>
+        <v>1670</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>24.88</v>
+        <v>4.7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>24.88</v>
+        <v>3.45</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CLPI.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1392,23 +1392,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1595</v>
+        <v>825</v>
       </c>
       <c r="D14" t="n">
-        <v>1650</v>
+        <v>815</v>
       </c>
       <c r="E14" t="n">
-        <v>1670</v>
+        <v>895</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.7</v>
+        <v>8.48</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.21</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>FMII.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1434,19 +1434,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>825</v>
+        <v>252</v>
       </c>
       <c r="D15" t="n">
-        <v>815</v>
+        <v>244</v>
       </c>
       <c r="E15" t="n">
-        <v>895</v>
+        <v>262</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.48</v>
+        <v>3.97</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.21</v>
+        <v>-3.17</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FMII.JK</t>
+          <t>IMAS.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1476,23 +1476,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>252</v>
+        <v>885</v>
       </c>
       <c r="D16" t="n">
-        <v>244</v>
+        <v>890</v>
       </c>
       <c r="E16" t="n">
-        <v>262</v>
+        <v>900</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.97</v>
+        <v>1.69</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.17</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IMAS.JK</t>
+          <t>INDY.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1518,19 +1518,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>885</v>
+        <v>2260</v>
       </c>
       <c r="D17" t="n">
-        <v>890</v>
+        <v>2370</v>
       </c>
       <c r="E17" t="n">
-        <v>900</v>
+        <v>2520</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.69</v>
+        <v>11.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.87</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INDY.JK</t>
+          <t>KARW.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1560,23 +1560,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2260</v>
+        <v>274</v>
       </c>
       <c r="D18" t="n">
-        <v>2370</v>
+        <v>274</v>
       </c>
       <c r="E18" t="n">
-        <v>2520</v>
+        <v>288</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>11.5</v>
+        <v>5.11</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1593,7 +1593,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KARW.JK</t>
+          <t>KBLV.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1602,23 +1602,23 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>274</v>
+        <v>97</v>
       </c>
       <c r="D19" t="n">
-        <v>274</v>
+        <v>102</v>
       </c>
       <c r="E19" t="n">
-        <v>288</v>
+        <v>107</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.11</v>
+        <v>10.31</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>5.15</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KBLV.JK</t>
+          <t>MAYA.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1644,19 +1644,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="D20" t="n">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="E20" t="n">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.31</v>
+        <v>7.53</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5.15</v>
+        <v>3.23</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MAYA.JK</t>
+          <t>MBSS.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1686,19 +1686,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>186</v>
+        <v>2540</v>
       </c>
       <c r="D21" t="n">
-        <v>192</v>
+        <v>2640</v>
       </c>
       <c r="E21" t="n">
-        <v>200</v>
+        <v>2690</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7.53</v>
+        <v>5.91</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.23</v>
+        <v>3.94</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MBSS.JK</t>
+          <t>MBTO.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1728,23 +1728,23 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2540</v>
+        <v>115</v>
       </c>
       <c r="D22" t="n">
-        <v>2640</v>
+        <v>113</v>
       </c>
       <c r="E22" t="n">
-        <v>2690</v>
+        <v>119</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.91</v>
+        <v>3.48</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.74</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MBTO.JK</t>
+          <t>MDLN.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1770,19 +1770,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="D23" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="E23" t="n">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.48</v>
+        <v>1.92</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.74</v>
+        <v>-1.92</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MDLN.JK</t>
+          <t>MEGA.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1812,23 +1812,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>52</v>
+        <v>2010</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>2100</v>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>2100</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.92</v>
+        <v>4.48</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.48</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MEGA.JK</t>
+          <t>MLPT.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1854,23 +1854,23 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2010</v>
+        <v>20200</v>
       </c>
       <c r="D25" t="n">
-        <v>2100</v>
+        <v>20000</v>
       </c>
       <c r="E25" t="n">
-        <v>2100</v>
+        <v>20800</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.48</v>
+        <v>2.97</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.99</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MLPT.JK</t>
+          <t>OMRE.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20200</v>
+        <v>1075</v>
       </c>
       <c r="D26" t="n">
-        <v>20000</v>
+        <v>1025</v>
       </c>
       <c r="E26" t="n">
-        <v>20800</v>
+        <v>1100</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.99</v>
+        <v>-4.65</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1938,23 +1938,23 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1075</v>
+        <v>3750</v>
       </c>
       <c r="D27" t="n">
-        <v>1025</v>
+        <v>3850</v>
       </c>
       <c r="E27" t="n">
-        <v>1100</v>
+        <v>4080</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.65</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.67</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>RUIS.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1980,19 +1980,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3750</v>
+        <v>186</v>
       </c>
       <c r="D28" t="n">
-        <v>3850</v>
+        <v>189</v>
       </c>
       <c r="E28" t="n">
-        <v>4080</v>
+        <v>208</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>11.83</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.67</v>
+        <v>1.61</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RUIS.JK</t>
+          <t>SMRA.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>186</v>
+        <v>302</v>
       </c>
       <c r="D29" t="n">
-        <v>189</v>
+        <v>308</v>
       </c>
       <c r="E29" t="n">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>11.83</v>
+        <v>3.31</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SMRA.JK</t>
+          <t>TIRA.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2064,23 +2064,23 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>302</v>
+        <v>665</v>
       </c>
       <c r="D30" t="n">
-        <v>308</v>
+        <v>660</v>
       </c>
       <c r="E30" t="n">
-        <v>312</v>
+        <v>665</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.75</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TIRA.JK</t>
+          <t>TIRT.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2106,23 +2106,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>665</v>
+        <v>525</v>
       </c>
       <c r="D31" t="n">
-        <v>660</v>
+        <v>530</v>
       </c>
       <c r="E31" t="n">
-        <v>665</v>
+        <v>550</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.95</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TIRT.JK</t>
+          <t>TMPO.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2148,23 +2148,23 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>525</v>
+        <v>130</v>
       </c>
       <c r="D32" t="n">
-        <v>530</v>
+        <v>119</v>
       </c>
       <c r="E32" t="n">
-        <v>550</v>
+        <v>130</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TMPO.JK</t>
+          <t>WTON.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2190,19 +2190,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="D33" t="n">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="E33" t="n">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="F33" s="4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G33" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>-8.460000000000001</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WTON.JK</t>
+          <t>YULE.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2232,16 +2232,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>78</v>
+        <v>3540</v>
       </c>
       <c r="D34" t="n">
-        <v>78</v>
+        <v>3540</v>
       </c>
       <c r="E34" t="n">
-        <v>81</v>
+        <v>3540</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>YULE.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2274,23 +2274,23 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3540</v>
+        <v>1535</v>
       </c>
       <c r="D35" t="n">
-        <v>3540</v>
+        <v>1845</v>
       </c>
       <c r="E35" t="n">
-        <v>3540</v>
+        <v>1845</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>20.2</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2307,7 +2307,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CASA.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2316,19 +2316,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1535</v>
+        <v>850</v>
       </c>
       <c r="D36" t="n">
-        <v>1845</v>
+        <v>885</v>
       </c>
       <c r="E36" t="n">
-        <v>1845</v>
+        <v>895</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>20.2</v>
+        <v>5.29</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>20.2</v>
+        <v>4.12</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>KIOS.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2358,23 +2358,23 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>850</v>
+        <v>91</v>
       </c>
       <c r="D37" t="n">
-        <v>885</v>
+        <v>86</v>
       </c>
       <c r="E37" t="n">
-        <v>895</v>
+        <v>97</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5.29</v>
+        <v>6.59</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-5.49</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KIOS.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2400,23 +2400,23 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D38" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E38" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6.59</v>
+        <v>11.83</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-5.49</v>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.23</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2442,23 +2442,23 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="D39" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="E39" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>11.83</v>
+        <v>5.34</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-5.34</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2475,7 +2475,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>HELI.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2484,23 +2484,23 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="D40" t="n">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="E40" t="n">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5.34</v>
+        <v>4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-5.34</v>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.57</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HELI.JK</t>
+          <t>GHON.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2526,19 +2526,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>175</v>
+        <v>1925</v>
       </c>
       <c r="D41" t="n">
-        <v>176</v>
+        <v>2330</v>
       </c>
       <c r="E41" t="n">
-        <v>182</v>
+        <v>2400</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4</v>
+        <v>24.68</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.57</v>
+        <v>21.04</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GHON.JK</t>
+          <t>RISE.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2568,23 +2568,23 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1925</v>
+        <v>1190</v>
       </c>
       <c r="D42" t="n">
-        <v>2330</v>
+        <v>1175</v>
       </c>
       <c r="E42" t="n">
-        <v>2400</v>
+        <v>1260</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>24.68</v>
+        <v>5.88</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>21.04</v>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.26</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2601,7 +2601,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RISE.JK</t>
+          <t>MGRO.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2610,23 +2610,23 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1190</v>
+        <v>685</v>
       </c>
       <c r="D43" t="n">
-        <v>1175</v>
+        <v>690</v>
       </c>
       <c r="E43" t="n">
-        <v>1260</v>
+        <v>715</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5.88</v>
+        <v>4.38</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.73</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MGRO.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2652,19 +2652,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>685</v>
+        <v>73</v>
       </c>
       <c r="D44" t="n">
-        <v>690</v>
+        <v>76</v>
       </c>
       <c r="E44" t="n">
-        <v>715</v>
+        <v>80</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4.38</v>
+        <v>9.59</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.73</v>
+        <v>4.11</v>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>SATU.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2694,23 +2694,23 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>73</v>
+        <v>272</v>
       </c>
       <c r="D45" t="n">
-        <v>76</v>
+        <v>272</v>
       </c>
       <c r="E45" t="n">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>9.59</v>
+        <v>0.74</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SATU.JK</t>
+          <t>SFAN.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2736,23 +2736,23 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>272</v>
+        <v>1970</v>
       </c>
       <c r="D46" t="n">
-        <v>272</v>
+        <v>1980</v>
       </c>
       <c r="E46" t="n">
-        <v>274</v>
+        <v>1985</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.51</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2769,7 +2769,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SFAN.JK</t>
+          <t>POLU.JK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2778,19 +2778,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1970</v>
+        <v>14025</v>
       </c>
       <c r="D47" t="n">
-        <v>1980</v>
+        <v>16225</v>
       </c>
       <c r="E47" t="n">
-        <v>1985</v>
+        <v>16650</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.76</v>
+        <v>18.72</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.51</v>
+        <v>15.69</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>POLU.JK</t>
+          <t>CSRA.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2820,19 +2820,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14025</v>
+        <v>785</v>
       </c>
       <c r="D48" t="n">
-        <v>16225</v>
+        <v>810</v>
       </c>
       <c r="E48" t="n">
-        <v>16650</v>
+        <v>840</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>18.72</v>
+        <v>7.01</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>15.69</v>
+        <v>3.18</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CSRA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2862,23 +2862,23 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>785</v>
+        <v>406</v>
       </c>
       <c r="D49" t="n">
-        <v>810</v>
+        <v>406</v>
       </c>
       <c r="E49" t="n">
-        <v>840</v>
+        <v>416</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>7.01</v>
+        <v>2.46</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>PADA.JK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>406</v>
+        <v>127</v>
       </c>
       <c r="D50" t="n">
-        <v>406</v>
+        <v>127</v>
       </c>
       <c r="E50" t="n">
-        <v>416</v>
+        <v>134</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2.46</v>
+        <v>5.51</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PADA.JK</t>
+          <t>WINE.JK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2946,23 +2946,23 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D51" t="n">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="E51" t="n">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>5.51</v>
+        <v>4.65</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.49</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WINE.JK</t>
+          <t>VAST.JK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2988,23 +2988,23 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="D52" t="n">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="E52" t="n">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4.65</v>
+        <v>2.52</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.68</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VAST.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3030,23 +3030,23 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>119</v>
+        <v>442</v>
       </c>
       <c r="D53" t="n">
-        <v>117</v>
+        <v>505</v>
       </c>
       <c r="E53" t="n">
-        <v>122</v>
+        <v>520</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2.52</v>
+        <v>17.65</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>14.25</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3063,7 +3063,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3072,19 +3072,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>442</v>
+        <v>206</v>
       </c>
       <c r="D54" t="n">
-        <v>505</v>
+        <v>208</v>
       </c>
       <c r="E54" t="n">
-        <v>520</v>
+        <v>228</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>17.65</v>
+        <v>10.68</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>14.25</v>
+        <v>0.97</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3114,19 +3114,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>206</v>
+        <v>615</v>
       </c>
       <c r="D55" t="n">
-        <v>208</v>
+        <v>620</v>
       </c>
       <c r="E55" t="n">
-        <v>228</v>
+        <v>625</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.68</v>
+        <v>1.63</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>RSCH.JK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3156,23 +3156,23 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>615</v>
+        <v>316</v>
       </c>
       <c r="D56" t="n">
-        <v>620</v>
+        <v>316</v>
       </c>
       <c r="E56" t="n">
-        <v>625</v>
+        <v>326</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1.63</v>
+        <v>3.16</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3189,7 +3189,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>BREN.JK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3198,23 +3198,23 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>316</v>
+        <v>4080</v>
       </c>
       <c r="D57" t="n">
-        <v>316</v>
+        <v>4250</v>
       </c>
       <c r="E57" t="n">
-        <v>326</v>
+        <v>4460</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3.16</v>
+        <v>9.31</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.17</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3231,7 +3231,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>UDNG.JK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3240,19 +3240,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4080</v>
+        <v>1400</v>
       </c>
       <c r="D58" t="n">
-        <v>4250</v>
+        <v>1410</v>
       </c>
       <c r="E58" t="n">
-        <v>4460</v>
+        <v>1480</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>9.31</v>
+        <v>5.71</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>4.17</v>
+        <v>0.71</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UDNG.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3282,19 +3282,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1400</v>
+        <v>332</v>
       </c>
       <c r="D59" t="n">
-        <v>1410</v>
+        <v>340</v>
       </c>
       <c r="E59" t="n">
-        <v>1480</v>
+        <v>344</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>5.71</v>
+        <v>3.61</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>0.71</v>
+        <v>2.41</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>GRPH.JK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3324,19 +3324,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>332</v>
+        <v>61</v>
       </c>
       <c r="D60" t="n">
-        <v>340</v>
+        <v>63</v>
       </c>
       <c r="E60" t="n">
-        <v>344</v>
+        <v>64</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3.61</v>
+        <v>4.92</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>2.41</v>
+        <v>3.28</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GRPH.JK</t>
+          <t>UNTD.JK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3366,19 +3366,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D61" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E61" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>4.92</v>
+        <v>7.04</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>3.28</v>
+        <v>1.41</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>UNTD.JK</t>
+          <t>LIVE.JK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3408,23 +3408,23 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="D62" t="n">
-        <v>72</v>
+        <v>242</v>
       </c>
       <c r="E62" t="n">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-3.2</v>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3441,7 +3441,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LIVE.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3450,19 +3450,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>250</v>
+        <v>680</v>
       </c>
       <c r="D63" t="n">
-        <v>242</v>
+        <v>645</v>
       </c>
       <c r="E63" t="n">
-        <v>250</v>
+        <v>840</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0</v>
+        <v>23.53</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-3.2</v>
+        <v>-5.15</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3492,23 +3492,23 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>680</v>
+        <v>1180</v>
       </c>
       <c r="D64" t="n">
-        <v>645</v>
+        <v>1185</v>
       </c>
       <c r="E64" t="n">
-        <v>840</v>
+        <v>1260</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>23.53</v>
+        <v>6.78</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-5.15</v>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.42</v>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3525,7 +3525,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BATR.JK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3534,19 +3534,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1180</v>
+        <v>84</v>
       </c>
       <c r="D65" t="n">
-        <v>1185</v>
+        <v>86</v>
       </c>
       <c r="E65" t="n">
-        <v>1260</v>
+        <v>87</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>6.78</v>
+        <v>3.57</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>0.42</v>
+        <v>2.38</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BATR.JK</t>
+          <t>SPRE.JK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3576,19 +3576,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D66" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E66" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3.57</v>
+        <v>9.59</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>2.38</v>
+        <v>9.59</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SPRE.JK</t>
+          <t>PART.JK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3618,19 +3618,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="D67" t="n">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="E67" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>9.59</v>
+        <v>14</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>9.59</v>
+        <v>7</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PART.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3660,19 +3660,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>100</v>
+        <v>560</v>
       </c>
       <c r="D68" t="n">
-        <v>107</v>
+        <v>600</v>
       </c>
       <c r="E68" t="n">
-        <v>114</v>
+        <v>600</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>14</v>
+        <v>7.14</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>MDIY.JK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3702,23 +3702,23 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>560</v>
+        <v>850</v>
       </c>
       <c r="D69" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E69" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>7.14</v>
+        <v>5.88</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3735,7 +3735,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MDIY.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3744,23 +3744,23 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>850</v>
+        <v>4710</v>
       </c>
       <c r="D70" t="n">
-        <v>850</v>
+        <v>4890</v>
       </c>
       <c r="E70" t="n">
-        <v>900</v>
+        <v>5125</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>5.88</v>
+        <v>8.81</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.82</v>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3777,7 +3777,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>YOII.JK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4710</v>
+        <v>90</v>
       </c>
       <c r="D71" t="n">
-        <v>4890</v>
+        <v>91</v>
       </c>
       <c r="E71" t="n">
-        <v>5125</v>
+        <v>94</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>8.81</v>
+        <v>4.44</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>3.82</v>
+        <v>1.11</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>YOII.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3828,19 +3828,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>90</v>
+        <v>3755</v>
       </c>
       <c r="D72" t="n">
-        <v>91</v>
+        <v>3860</v>
       </c>
       <c r="E72" t="n">
-        <v>94</v>
+        <v>4000</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>4.44</v>
+        <v>6.52</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3870,23 +3870,23 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3755</v>
+        <v>216</v>
       </c>
       <c r="D73" t="n">
-        <v>3860</v>
+        <v>197</v>
       </c>
       <c r="E73" t="n">
-        <v>4000</v>
+        <v>228</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>6.52</v>
+        <v>5.56</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3903,7 +3903,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ASPR.JK</t>
+          <t>RLCO.JK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3912,23 +3912,23 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>216</v>
+        <v>3020</v>
       </c>
       <c r="D74" t="n">
-        <v>197</v>
+        <v>3500</v>
       </c>
       <c r="E74" t="n">
-        <v>228</v>
+        <v>3710</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>5.56</v>
+        <v>22.85</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>15.89</v>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3945,7 +3945,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RLCO.JK</t>
+          <t>YUPI.JK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3954,19 +3954,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3020</v>
+        <v>1435</v>
       </c>
       <c r="D75" t="n">
-        <v>3500</v>
+        <v>1480</v>
       </c>
       <c r="E75" t="n">
-        <v>3710</v>
+        <v>1505</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>22.85</v>
+        <v>4.88</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>15.89</v>
+        <v>3.14</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>YUPI.JK</t>
+          <t>AIMS.JK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1435</v>
+        <v>390</v>
       </c>
       <c r="D76" t="n">
-        <v>1480</v>
+        <v>410</v>
       </c>
       <c r="E76" t="n">
-        <v>1505</v>
+        <v>446</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>4.88</v>
+        <v>14.36</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>3.14</v>
+        <v>5.13</v>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AIMS.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4038,23 +4038,23 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>390</v>
+        <v>640</v>
       </c>
       <c r="D77" t="n">
-        <v>410</v>
+        <v>610</v>
       </c>
       <c r="E77" t="n">
-        <v>446</v>
+        <v>640</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>14.36</v>
+        <v>0</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-4.69</v>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VICI.JK</t>
+          <t>LUCY.JK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4080,23 +4080,23 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>640</v>
+        <v>1490</v>
       </c>
       <c r="D78" t="n">
-        <v>610</v>
+        <v>1535</v>
       </c>
       <c r="E78" t="n">
-        <v>640</v>
+        <v>1545</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.02</v>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4113,7 +4113,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LUCY.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4122,19 +4122,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1490</v>
+        <v>610</v>
       </c>
       <c r="D79" t="n">
-        <v>1535</v>
+        <v>630</v>
       </c>
       <c r="E79" t="n">
-        <v>1545</v>
+        <v>665</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>3.69</v>
+        <v>9.02</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4164,23 +4164,23 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>610</v>
+        <v>202</v>
       </c>
       <c r="D80" t="n">
-        <v>630</v>
+        <v>197</v>
       </c>
       <c r="E80" t="n">
-        <v>665</v>
+        <v>204</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>9.02</v>
+        <v>0.99</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-2.48</v>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4197,7 +4197,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>CMNT.JK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4206,19 +4206,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>202</v>
+        <v>815</v>
       </c>
       <c r="D81" t="n">
-        <v>197</v>
+        <v>815</v>
       </c>
       <c r="E81" t="n">
-        <v>204</v>
+        <v>825</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>-2.48</v>
+        <v>0</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CMNT.JK</t>
+          <t>BOBA.JK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4248,19 +4248,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>815</v>
+        <v>336</v>
       </c>
       <c r="D82" t="n">
-        <v>815</v>
+        <v>330</v>
       </c>
       <c r="E82" t="n">
-        <v>825</v>
+        <v>350</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1.23</v>
+        <v>4.17</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>BSML.JK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4290,23 +4290,23 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>336</v>
+        <v>428</v>
       </c>
       <c r="D83" t="n">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="E83" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>4.17</v>
+        <v>5.14</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>5.14</v>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4323,7 +4323,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4332,19 +4332,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>428</v>
+        <v>330</v>
       </c>
       <c r="D84" t="n">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="E84" t="n">
-        <v>450</v>
+        <v>346</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>5.14</v>
+        <v>4.85</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>5.14</v>
+        <v>3.03</v>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4374,23 +4374,23 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>330</v>
+        <v>2890</v>
       </c>
       <c r="D85" t="n">
-        <v>340</v>
+        <v>2880</v>
       </c>
       <c r="E85" t="n">
-        <v>346</v>
+        <v>2880</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>4.85</v>
+        <v>-0.35</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.35</v>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">

--- a/data/performance/daily/signal_list_2026-06-15.xlsx
+++ b/data/performance/daily/signal_list_2026-06-15.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-15.xlsx
+++ b/data/performance/daily/signal_list_2026-06-15.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>-5.34</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-5.15</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -815,12 +851,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-1.79</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -899,12 +945,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -921,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -931,9 +982,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -963,7 +1015,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -988,15 +1040,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1033,12 +1090,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1075,12 +1137,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1112,17 +1179,22 @@
       <c r="G7" s="4" t="n">
         <v>-3.76</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1154,17 +1226,22 @@
       <c r="G8" s="4" t="n">
         <v>-1.18</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1201,12 +1278,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1238,17 +1320,22 @@
       <c r="G10" s="4" t="n">
         <v>-0.31</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1285,12 +1372,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1327,12 +1419,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1369,12 +1466,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1406,17 +1508,22 @@
       <c r="G14" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1448,17 +1555,22 @@
       <c r="G15" s="4" t="n">
         <v>-3.17</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1495,12 +1607,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1537,12 +1654,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1574,17 +1696,22 @@
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1621,12 +1748,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1663,12 +1795,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1705,12 +1842,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1742,17 +1884,22 @@
       <c r="G22" s="4" t="n">
         <v>-1.74</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1784,17 +1931,22 @@
       <c r="G23" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1831,12 +1983,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1868,17 +2025,22 @@
       <c r="G25" s="4" t="n">
         <v>-0.99</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1910,17 +2072,22 @@
       <c r="G26" s="4" t="n">
         <v>-4.65</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1957,12 +2124,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1999,12 +2171,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2041,12 +2218,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2083,12 +2265,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2125,12 +2312,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2167,12 +2359,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2204,17 +2401,22 @@
       <c r="G33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2251,12 +2453,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2293,12 +2500,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2335,12 +2547,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2372,17 +2589,22 @@
       <c r="G37" s="4" t="n">
         <v>-5.49</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2419,12 +2641,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2456,17 +2683,22 @@
       <c r="G39" s="4" t="n">
         <v>-5.34</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2503,12 +2735,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2545,12 +2782,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2582,17 +2824,22 @@
       <c r="G42" s="4" t="n">
         <v>-1.26</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2629,12 +2876,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2671,12 +2923,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2708,17 +2965,22 @@
       <c r="G45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2755,12 +3017,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2797,12 +3064,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2839,12 +3111,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2876,17 +3153,22 @@
       <c r="G49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2918,17 +3200,22 @@
       <c r="G50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2965,12 +3252,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3002,17 +3294,22 @@
       <c r="G52" s="4" t="n">
         <v>-1.68</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3049,12 +3346,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3091,12 +3393,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3133,12 +3440,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3170,17 +3482,22 @@
       <c r="G56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3217,12 +3534,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3259,12 +3581,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3301,12 +3628,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3343,12 +3675,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3385,12 +3722,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3427,12 +3769,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3464,17 +3811,22 @@
       <c r="G63" s="4" t="n">
         <v>-5.15</v>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3511,12 +3863,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3553,12 +3910,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3595,12 +3957,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3637,12 +4004,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3679,12 +4051,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3716,17 +4093,22 @@
       <c r="G69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3763,12 +4145,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3805,12 +4192,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,12 +4239,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3884,17 +4281,22 @@
       <c r="G73" s="4" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3931,12 +4333,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3973,12 +4380,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4015,12 +4427,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4057,12 +4474,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4099,12 +4521,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4141,12 +4568,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4178,17 +4610,22 @@
       <c r="G80" s="4" t="n">
         <v>-2.48</v>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4220,17 +4657,22 @@
       <c r="G81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4262,17 +4704,22 @@
       <c r="G82" s="4" t="n">
         <v>-1.79</v>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4309,12 +4756,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4351,12 +4803,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4393,12 +4850,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-15.xlsx
+++ b/data/performance/daily/signal_list_2026-06-15.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>1490</v>
       </c>
       <c r="D5" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E5" t="n">
         <v>1475</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1490</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-1.01</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>2540</v>
       </c>
       <c r="D6" t="n">
+        <v>2570</v>
+      </c>
+      <c r="E6" t="n">
         <v>2640</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2690</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>5.91</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>3.94</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>850</v>
       </c>
       <c r="D7" t="n">
+        <v>845</v>
+      </c>
+      <c r="E7" t="n">
         <v>885</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>895</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>5.29</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>4.12</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>131</v>
       </c>
       <c r="D8" t="n">
+        <v>119</v>
+      </c>
+      <c r="E8" t="n">
         <v>124</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>138</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>5.34</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-5.34</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>680</v>
       </c>
       <c r="D9" t="n">
+        <v>700</v>
+      </c>
+      <c r="E9" t="n">
         <v>645</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>840</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>23.53</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-5.15</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>560</v>
       </c>
       <c r="D10" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="E10" t="n">
         <v>600</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>7.14</v>
+      <c r="F10" t="n">
+        <v>600</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H10" s="4" t="n">
+        <v>7.14</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>8500</v>
       </c>
       <c r="D11" t="n">
+        <v>8100</v>
+      </c>
+      <c r="E11" t="n">
         <v>8700</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>9125</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>7.35</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>2.35</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>336</v>
       </c>
       <c r="D12" t="n">
+        <v>338</v>
+      </c>
+      <c r="E12" t="n">
         <v>330</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>350</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-1.79</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>428</v>
       </c>
       <c r="D13" t="n">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="E13" t="n">
         <v>450</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>5.14</v>
+      <c r="F13" t="n">
+        <v>450</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>5.14</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H13" s="4" t="n">
+        <v>5.14</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -972,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -980,12 +1013,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1015,45 +1049,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1079,28 +1118,31 @@
       <c r="E5" t="n">
         <v>2880</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>-0.35</v>
+      <c r="F5" t="n">
+        <v>2880</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>-0.35</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1126,28 +1168,31 @@
       <c r="E6" t="n">
         <v>2880</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>-0.35</v>
+      <c r="F6" t="n">
+        <v>2880</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>-0.35</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1168,33 +1213,36 @@
         <v>505</v>
       </c>
       <c r="D7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" t="n">
         <v>486</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>520</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.97</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-3.76</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>850</v>
       </c>
       <c r="D8" t="n">
+        <v>870</v>
+      </c>
+      <c r="E8" t="n">
         <v>840</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>875</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>2.94</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-1.18</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>155</v>
       </c>
       <c r="D9" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E9" t="n">
         <v>159</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>2.58</v>
+      <c r="F9" t="n">
+        <v>159</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>2.58</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H9" s="4" t="n">
+        <v>2.58</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>3220</v>
       </c>
       <c r="D10" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E10" t="n">
         <v>3210</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>3450</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.31</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>272</v>
       </c>
       <c r="D11" t="n">
+        <v>272</v>
+      </c>
+      <c r="E11" t="n">
         <v>268</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>272</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-1.47</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>1005</v>
       </c>
       <c r="D12" t="n">
-        <v>1255</v>
+        <v>1170</v>
       </c>
       <c r="E12" t="n">
         <v>1255</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>24.88</v>
+      <c r="F12" t="n">
+        <v>1255</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>24.88</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H12" s="4" t="n">
+        <v>24.88</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>1595</v>
       </c>
       <c r="D13" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E13" t="n">
         <v>1650</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1670</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>3.45</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>825</v>
       </c>
       <c r="D14" t="n">
+        <v>875</v>
+      </c>
+      <c r="E14" t="n">
         <v>815</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>895</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>8.48</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>252</v>
       </c>
       <c r="D15" t="n">
+        <v>254</v>
+      </c>
+      <c r="E15" t="n">
         <v>244</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>262</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>3.97</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-3.17</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1594,30 +1666,33 @@
         <v>890</v>
       </c>
       <c r="E16" t="n">
+        <v>890</v>
+      </c>
+      <c r="F16" t="n">
         <v>900</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.69</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>2260</v>
       </c>
       <c r="D17" t="n">
+        <v>2330</v>
+      </c>
+      <c r="E17" t="n">
         <v>2370</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>2520</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>4.87</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1688,30 +1766,33 @@
         <v>274</v>
       </c>
       <c r="E18" t="n">
+        <v>274</v>
+      </c>
+      <c r="F18" t="n">
         <v>288</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>5.11</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1732,33 +1813,36 @@
         <v>97</v>
       </c>
       <c r="D19" t="n">
+        <v>98</v>
+      </c>
+      <c r="E19" t="n">
         <v>102</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>107</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>10.31</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>5.15</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>186</v>
       </c>
       <c r="D20" t="n">
+        <v>188</v>
+      </c>
+      <c r="E20" t="n">
         <v>192</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>200</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>7.53</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>3.23</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>2540</v>
       </c>
       <c r="D21" t="n">
+        <v>2570</v>
+      </c>
+      <c r="E21" t="n">
         <v>2640</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>2690</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>5.91</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>3.94</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>115</v>
       </c>
       <c r="D22" t="n">
+        <v>115</v>
+      </c>
+      <c r="E22" t="n">
         <v>113</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>119</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>3.48</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-1.74</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1923,30 +2016,33 @@
         <v>51</v>
       </c>
       <c r="E23" t="n">
+        <v>51</v>
+      </c>
+      <c r="F23" t="n">
         <v>53</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>2010</v>
       </c>
       <c r="D24" t="n">
-        <v>2100</v>
+        <v>2010</v>
       </c>
       <c r="E24" t="n">
         <v>2100</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>4.48</v>
+      <c r="F24" t="n">
+        <v>2100</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>4.48</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H24" s="4" t="n">
+        <v>4.48</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>20200</v>
       </c>
       <c r="D25" t="n">
+        <v>20200</v>
+      </c>
+      <c r="E25" t="n">
         <v>20000</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>20800</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>2.97</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-0.99</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>1075</v>
       </c>
       <c r="D26" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E26" t="n">
         <v>1025</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>1100</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>2.33</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-4.65</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>3750</v>
       </c>
       <c r="D27" t="n">
+        <v>3880</v>
+      </c>
+      <c r="E27" t="n">
         <v>3850</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>4080</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>2.67</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2155,33 +2263,36 @@
         <v>186</v>
       </c>
       <c r="D28" t="n">
+        <v>187</v>
+      </c>
+      <c r="E28" t="n">
         <v>189</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>208</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>11.83</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>302</v>
       </c>
       <c r="D29" t="n">
+        <v>310</v>
+      </c>
+      <c r="E29" t="n">
         <v>308</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>312</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>3.31</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>665</v>
       </c>
       <c r="D30" t="n">
+        <v>665</v>
+      </c>
+      <c r="E30" t="n">
         <v>660</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>665</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-0.75</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>525</v>
       </c>
       <c r="D31" t="n">
+        <v>525</v>
+      </c>
+      <c r="E31" t="n">
         <v>530</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>550</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>4.76</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>130</v>
       </c>
       <c r="D32" t="n">
+        <v>123</v>
+      </c>
+      <c r="E32" t="n">
         <v>119</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>130</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-8.460000000000001</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2393,30 +2516,33 @@
         <v>78</v>
       </c>
       <c r="E33" t="n">
+        <v>78</v>
+      </c>
+      <c r="F33" t="n">
         <v>81</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>3.85</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2442,28 +2568,31 @@
       <c r="E34" t="n">
         <v>3540</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>0</v>
+      <c r="F34" t="n">
+        <v>3540</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>1535</v>
       </c>
       <c r="D35" t="n">
-        <v>1845</v>
+        <v>1535</v>
       </c>
       <c r="E35" t="n">
         <v>1845</v>
       </c>
-      <c r="F35" s="4" t="n">
-        <v>20.2</v>
+      <c r="F35" t="n">
+        <v>1845</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>20.2</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H35" s="4" t="n">
+        <v>20.2</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>850</v>
       </c>
       <c r="D36" t="n">
+        <v>845</v>
+      </c>
+      <c r="E36" t="n">
         <v>885</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>895</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>5.29</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>4.12</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>91</v>
       </c>
       <c r="D37" t="n">
+        <v>83</v>
+      </c>
+      <c r="E37" t="n">
         <v>86</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>97</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>6.59</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-5.49</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>93</v>
       </c>
       <c r="D38" t="n">
+        <v>95</v>
+      </c>
+      <c r="E38" t="n">
         <v>96</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>104</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>11.83</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>3.23</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>131</v>
       </c>
       <c r="D39" t="n">
+        <v>119</v>
+      </c>
+      <c r="E39" t="n">
         <v>124</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>138</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>5.34</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>-5.34</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>175</v>
       </c>
       <c r="D40" t="n">
+        <v>179</v>
+      </c>
+      <c r="E40" t="n">
         <v>176</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>182</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>1925</v>
       </c>
       <c r="D41" t="n">
+        <v>1930</v>
+      </c>
+      <c r="E41" t="n">
         <v>2330</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>2400</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>24.68</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>21.04</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>1190</v>
       </c>
       <c r="D42" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E42" t="n">
         <v>1175</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>1260</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>5.88</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-1.26</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>685</v>
       </c>
       <c r="D43" t="n">
+        <v>685</v>
+      </c>
+      <c r="E43" t="n">
         <v>690</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>715</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>4.38</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2907,33 +3063,36 @@
         <v>73</v>
       </c>
       <c r="D44" t="n">
+        <v>73</v>
+      </c>
+      <c r="E44" t="n">
         <v>76</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>80</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>9.59</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>4.11</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2957,30 +3116,33 @@
         <v>272</v>
       </c>
       <c r="E45" t="n">
+        <v>272</v>
+      </c>
+      <c r="F45" t="n">
         <v>274</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3001,33 +3163,36 @@
         <v>1970</v>
       </c>
       <c r="D46" t="n">
+        <v>1975</v>
+      </c>
+      <c r="E46" t="n">
         <v>1980</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>1985</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>0.51</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>14025</v>
       </c>
       <c r="D47" t="n">
+        <v>14700</v>
+      </c>
+      <c r="E47" t="n">
         <v>16225</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>16650</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>18.72</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>15.69</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>785</v>
       </c>
       <c r="D48" t="n">
+        <v>840</v>
+      </c>
+      <c r="E48" t="n">
         <v>810</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>840</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>7.01</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>3.18</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3145,30 +3316,33 @@
         <v>406</v>
       </c>
       <c r="E49" t="n">
+        <v>406</v>
+      </c>
+      <c r="F49" t="n">
         <v>416</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>2.46</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3189,33 +3363,36 @@
         <v>127</v>
       </c>
       <c r="D50" t="n">
+        <v>131</v>
+      </c>
+      <c r="E50" t="n">
         <v>127</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>134</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>5.51</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3236,33 +3413,36 @@
         <v>172</v>
       </c>
       <c r="D51" t="n">
+        <v>171</v>
+      </c>
+      <c r="E51" t="n">
         <v>178</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>180</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>4.65</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>3.49</v>
       </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3283,33 +3463,36 @@
         <v>119</v>
       </c>
       <c r="D52" t="n">
+        <v>120</v>
+      </c>
+      <c r="E52" t="n">
         <v>117</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>122</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>2.52</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>-1.68</v>
       </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,33 +3513,36 @@
         <v>442</v>
       </c>
       <c r="D53" t="n">
+        <v>446</v>
+      </c>
+      <c r="E53" t="n">
         <v>505</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>520</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>17.65</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>14.25</v>
       </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,33 +3563,36 @@
         <v>206</v>
       </c>
       <c r="D54" t="n">
+        <v>210</v>
+      </c>
+      <c r="E54" t="n">
         <v>208</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>228</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>10.68</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3424,33 +3613,36 @@
         <v>615</v>
       </c>
       <c r="D55" t="n">
+        <v>615</v>
+      </c>
+      <c r="E55" t="n">
         <v>620</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>625</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3471,33 +3663,36 @@
         <v>316</v>
       </c>
       <c r="D56" t="n">
+        <v>318</v>
+      </c>
+      <c r="E56" t="n">
         <v>316</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>326</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>3.16</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3518,33 +3713,36 @@
         <v>4080</v>
       </c>
       <c r="D57" t="n">
+        <v>4130</v>
+      </c>
+      <c r="E57" t="n">
         <v>4250</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>4460</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>9.31</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3565,33 +3763,36 @@
         <v>1400</v>
       </c>
       <c r="D58" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E58" t="n">
         <v>1410</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>1480</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>5.71</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3612,33 +3813,36 @@
         <v>332</v>
       </c>
       <c r="D59" t="n">
+        <v>332</v>
+      </c>
+      <c r="E59" t="n">
         <v>340</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>344</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>3.61</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>2.41</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3659,33 +3863,36 @@
         <v>61</v>
       </c>
       <c r="D60" t="n">
+        <v>64</v>
+      </c>
+      <c r="E60" t="n">
         <v>63</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>64</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>4.92</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>3.28</v>
       </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3706,33 +3913,36 @@
         <v>71</v>
       </c>
       <c r="D61" t="n">
+        <v>73</v>
+      </c>
+      <c r="E61" t="n">
         <v>72</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>76</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="G61" s="4" t="n">
         <v>7.04</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3753,33 +3963,36 @@
         <v>250</v>
       </c>
       <c r="D62" t="n">
+        <v>250</v>
+      </c>
+      <c r="E62" t="n">
         <v>242</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>250</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>-3.2</v>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,33 +4013,36 @@
         <v>680</v>
       </c>
       <c r="D63" t="n">
+        <v>700</v>
+      </c>
+      <c r="E63" t="n">
         <v>645</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>840</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="G63" s="4" t="n">
         <v>23.53</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>-5.15</v>
       </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,33 +4063,36 @@
         <v>1180</v>
       </c>
       <c r="D64" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E64" t="n">
         <v>1185</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>1260</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>6.78</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="H64" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3894,33 +4113,36 @@
         <v>84</v>
       </c>
       <c r="D65" t="n">
+        <v>84</v>
+      </c>
+      <c r="E65" t="n">
         <v>86</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>87</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="G65" s="4" t="n">
         <v>3.57</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>2.38</v>
       </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3941,33 +4163,36 @@
         <v>73</v>
       </c>
       <c r="D66" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E66" t="n">
         <v>80</v>
       </c>
-      <c r="F66" s="4" t="n">
-        <v>9.59</v>
+      <c r="F66" t="n">
+        <v>80</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>9.59</v>
       </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H66" s="4" t="n">
+        <v>9.59</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3988,33 +4213,36 @@
         <v>100</v>
       </c>
       <c r="D67" t="n">
+        <v>101</v>
+      </c>
+      <c r="E67" t="n">
         <v>107</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>114</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="G67" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4035,33 +4263,36 @@
         <v>560</v>
       </c>
       <c r="D68" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="E68" t="n">
         <v>600</v>
       </c>
-      <c r="F68" s="4" t="n">
-        <v>7.14</v>
+      <c r="F68" t="n">
+        <v>600</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H68" s="4" t="n">
+        <v>7.14</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4085,30 +4316,33 @@
         <v>850</v>
       </c>
       <c r="E69" t="n">
+        <v>850</v>
+      </c>
+      <c r="F69" t="n">
         <v>900</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="G69" s="4" t="n">
         <v>5.88</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="H69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4129,33 +4363,36 @@
         <v>4710</v>
       </c>
       <c r="D70" t="n">
+        <v>4900</v>
+      </c>
+      <c r="E70" t="n">
         <v>4890</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>5125</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="G70" s="4" t="n">
         <v>8.81</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>3.82</v>
       </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4179,30 +4416,33 @@
         <v>91</v>
       </c>
       <c r="E71" t="n">
+        <v>91</v>
+      </c>
+      <c r="F71" t="n">
         <v>94</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="G71" s="4" t="n">
         <v>4.44</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="H71" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4223,33 +4463,36 @@
         <v>3755</v>
       </c>
       <c r="D72" t="n">
+        <v>3810</v>
+      </c>
+      <c r="E72" t="n">
         <v>3860</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>4000</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="G72" s="4" t="n">
         <v>6.52</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="H72" s="4" t="n">
         <v>2.8</v>
       </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4270,33 +4513,36 @@
         <v>216</v>
       </c>
       <c r="D73" t="n">
+        <v>216</v>
+      </c>
+      <c r="E73" t="n">
         <v>197</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>228</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="G73" s="4" t="n">
         <v>5.56</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="H73" s="4" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4317,33 +4563,36 @@
         <v>3020</v>
       </c>
       <c r="D74" t="n">
+        <v>3080</v>
+      </c>
+      <c r="E74" t="n">
         <v>3500</v>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>3710</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="G74" s="4" t="n">
         <v>22.85</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <v>15.89</v>
       </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4364,33 +4613,36 @@
         <v>1435</v>
       </c>
       <c r="D75" t="n">
+        <v>1440</v>
+      </c>
+      <c r="E75" t="n">
         <v>1480</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>1505</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="G75" s="4" t="n">
         <v>4.88</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>3.14</v>
       </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4411,33 +4663,36 @@
         <v>390</v>
       </c>
       <c r="D76" t="n">
+        <v>390</v>
+      </c>
+      <c r="E76" t="n">
         <v>410</v>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>446</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="G76" s="4" t="n">
         <v>14.36</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="H76" s="4" t="n">
         <v>5.13</v>
       </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4458,33 +4713,36 @@
         <v>640</v>
       </c>
       <c r="D77" t="n">
+        <v>630</v>
+      </c>
+      <c r="E77" t="n">
         <v>610</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>640</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="G77" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="H77" s="4" t="n">
         <v>-4.69</v>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4505,33 +4763,36 @@
         <v>1490</v>
       </c>
       <c r="D78" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E78" t="n">
         <v>1535</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>1545</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="G78" s="4" t="n">
         <v>3.69</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="H78" s="4" t="n">
         <v>3.02</v>
       </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4552,33 +4813,36 @@
         <v>610</v>
       </c>
       <c r="D79" t="n">
+        <v>615</v>
+      </c>
+      <c r="E79" t="n">
         <v>630</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>665</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="G79" s="4" t="n">
         <v>9.02</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="H79" s="4" t="n">
         <v>3.28</v>
       </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4599,33 +4863,36 @@
         <v>202</v>
       </c>
       <c r="D80" t="n">
+        <v>202</v>
+      </c>
+      <c r="E80" t="n">
         <v>197</v>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>204</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="G80" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="H80" s="4" t="n">
         <v>-2.48</v>
       </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4646,33 +4913,36 @@
         <v>815</v>
       </c>
       <c r="D81" t="n">
+        <v>820</v>
+      </c>
+      <c r="E81" t="n">
         <v>815</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>825</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="G81" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="H81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4693,33 +4963,36 @@
         <v>336</v>
       </c>
       <c r="D82" t="n">
+        <v>338</v>
+      </c>
+      <c r="E82" t="n">
         <v>330</v>
       </c>
-      <c r="E82" t="n">
+      <c r="F82" t="n">
         <v>350</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="G82" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="H82" s="4" t="n">
         <v>-1.79</v>
       </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4740,33 +5013,36 @@
         <v>428</v>
       </c>
       <c r="D83" t="n">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="E83" t="n">
         <v>450</v>
       </c>
-      <c r="F83" s="4" t="n">
-        <v>5.14</v>
+      <c r="F83" t="n">
+        <v>450</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>5.14</v>
       </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H83" s="4" t="n">
+        <v>5.14</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4787,33 +5063,36 @@
         <v>330</v>
       </c>
       <c r="D84" t="n">
+        <v>332</v>
+      </c>
+      <c r="E84" t="n">
         <v>340</v>
       </c>
-      <c r="E84" t="n">
+      <c r="F84" t="n">
         <v>346</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="G84" s="4" t="n">
         <v>4.85</v>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="H84" s="4" t="n">
         <v>3.03</v>
       </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4839,28 +5118,31 @@
       <c r="E85" t="n">
         <v>2880</v>
       </c>
-      <c r="F85" s="4" t="n">
-        <v>-0.35</v>
+      <c r="F85" t="n">
+        <v>2880</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>-0.35</v>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" s="4" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
       <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
